--- a/samples/unit_economics_golden.xlsx
+++ b/samples/unit_economics_golden.xlsx
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="B12" s="9">
-        <f>B5*B6*B11</f>
+        <f>IF(B11="","",B5*B6*B11)</f>
         <v/>
       </c>
     </row>
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B13" s="10">
-        <f>IF(B8=0,"",B12/B8)</f>
+        <f>IF(OR(B8=0,B12=""),"",B12/B8)</f>
         <v/>
       </c>
     </row>
